--- a/VNEDU-CHUANHANXET.xlsx
+++ b/VNEDU-CHUANHANXET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodejs\thu-gui-phu-huynh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554716B7-AC73-4899-B2B7-51C44F6C783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9FD551-63A3-4BB9-81A4-2338DAA407B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
